--- a/游戏设计王/捕鱼游戏数学-PartIII-随机倍数与竞赛模型.xlsx
+++ b/游戏设计王/捕鱼游戏数学-PartIII-随机倍数与竞赛模型.xlsx
@@ -229,12 +229,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.000%"/>
+    <numFmt numFmtId="177" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -925,7 +926,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -986,6 +987,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1710,7 +1714,7 @@
       <c r="B8" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="37">
         <f>IF(OR(C7="",C6="",C6=0),"",C7/C6)</f>
         <v>0.018</v>
       </c>
@@ -1807,11 +1811,11 @@
       <c r="B12" s="9">
         <v>40</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="37">
         <f>IF(OR(B12="",B12=0),"",$C$7/B12)</f>
         <v>0.0225</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="38">
         <f>IF(OR(C12="",B12=""),"",B12*C12)</f>
         <v>0.9</v>
       </c>
@@ -1835,11 +1839,11 @@
       <c r="B13" s="9">
         <v>45</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="37">
         <f>IF(OR(B13="",B13=0),"",$C$7/B13)</f>
         <v>0.02</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="38">
         <f>IF(OR(C13="",B13=""),"",B13*C13)</f>
         <v>0.9</v>
       </c>
@@ -1863,11 +1867,11 @@
       <c r="B14" s="9">
         <v>50</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="37">
         <f>IF(OR(B14="",B14=0),"",$C$7/B14)</f>
         <v>0.018</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="38">
         <f>IF(OR(C14="",B14=""),"",B14*C14)</f>
         <v>0.9</v>
       </c>
@@ -1891,11 +1895,11 @@
       <c r="B15" s="9">
         <v>55</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="37">
         <f>IF(OR(B15="",B15=0),"",$C$7/B15)</f>
         <v>0.0163636363636364</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="38">
         <f>IF(OR(C15="",B15=""),"",B15*C15)</f>
         <v>0.9</v>
       </c>
@@ -1919,11 +1923,11 @@
       <c r="B16" s="9">
         <v>60</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="37">
         <f>IF(OR(B16="",B16=0),"",$C$7/B16)</f>
         <v>0.015</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="38">
         <f>IF(OR(C16="",B16=""),"",B16*C16)</f>
         <v>0.9</v>
       </c>
@@ -1947,11 +1951,11 @@
       <c r="B17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="37">
         <f>IF(COUNT(B12:B16)=0,"",$C$7/AVERAGE(B12:B16))</f>
         <v>0.018</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="38">
         <f>IF(COUNT(B12:B16)=0,"",AVERAGE(B12:B16)*C17)</f>
         <v>0.9</v>
       </c>
@@ -2136,7 +2140,7 @@
         <f>IF(E24="★",$D$27,0)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="37">
         <f>IF(OR(C24="",C24=0),"",F24/C24)</f>
         <v>0</v>
       </c>
@@ -2166,7 +2170,7 @@
         <f>IF(E25="★",$D$27,0)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="37">
         <f>IF(OR(C25="",C25=0),"",F25/C25)</f>
         <v>0</v>
       </c>
@@ -2196,7 +2200,7 @@
         <f>IF(E26="★",$D$27,0)</f>
         <v>5.55</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="37">
         <f>IF(OR(C26="",C26=0),"",F26/C26)</f>
         <v>0.00555</v>
       </c>
